--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T10:23:38+00:00</t>
+    <t>2025-02-24T13:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:55:23+00:00</t>
+    <t>2025-02-26T08:56:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T08:56:44+00:00</t>
+    <t>2025-03-04T11:06:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T11:06:18+00:00</t>
+    <t>2025-03-06T12:24:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T12:24:43+00:00</t>
+    <t>2025-03-20T12:28:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-20T12:28:15+00:00</t>
+    <t>2025-03-24T06:28:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-device</t>
+    <t>https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-device</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T06:28:05+00:00</t>
+    <t>2025-03-24T07:27:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1044,7 +1044,7 @@
     <t>Device.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-patient)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient)
 </t>
   </si>
   <si>
@@ -1488,7 +1488,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="89.3984375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="69.87109375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T07:27:46+00:00</t>
+    <t>2025-03-24T07:43:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-18T10:23:29+00:00</t>
+    <t>2026-01-28T10:05:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1069,7 +1069,7 @@
     <t>Device.owner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization)
 </t>
   </si>
   <si>
@@ -1169,7 +1169,7 @@
     <t>Device.parent</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-device)
 </t>
   </si>
   <si>
@@ -1499,7 +1499,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="59.90234375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="64.109375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T10:05:57+00:00</t>
+    <t>2026-01-29T06:33:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T06:33:09+00:00</t>
+    <t>2026-02-03T10:06:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:06:44+00:00</t>
+    <t>2026-02-03T10:34:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:34:36+00:00</t>
+    <t>2026-02-09T07:50:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T07:50:08+00:00</t>
+    <t>2026-02-13T12:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T12:44:21+00:00</t>
+    <t>2026-02-16T08:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T08:31:54+00:00</t>
+    <t>2026-02-16T11:13:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T11:13:42+00:00</t>
+    <t>2026-02-17T09:00:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-device.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T09:00:43+00:00</t>
+    <t>2026-09-01T07:40:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
